--- a/Result/profitability/1587.xlsx
+++ b/Result/profitability/1587.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1325</v>
+        <v>0.1275</v>
       </c>
       <c r="N2" t="n">
-        <v>20.56375</v>
+        <v>20.0125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2225</v>
+        <v>0.21125</v>
       </c>
       <c r="N3" t="n">
-        <v>20.8325</v>
+        <v>20.77625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.28</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2625</v>
+        <v>0.2450000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>21.5925</v>
+        <v>21.44875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
         <v>98.2</v>
@@ -1018,10 +1018,10 @@
         <v>0.37</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3075000000000001</v>
+        <v>0.2837500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>22.40875</v>
+        <v>22.15125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>98.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.87</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4087500000000001</v>
+        <v>0.3700000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>23.17375</v>
+        <v>23.10875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1161,7 +1161,7 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>99.2</v>
@@ -1264,10 +1264,10 @@
         <v>1.34</v>
       </c>
       <c r="M7" t="n">
-        <v>0.55375</v>
+        <v>0.52125</v>
       </c>
       <c r="N7" t="n">
-        <v>24.0275</v>
+        <v>24.05125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>99.40000000000001</v>
@@ -7671,6 +7671,133 @@
       </c>
       <c r="AM57" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>598</v>
+      </c>
+      <c r="D58" t="n">
+        <v>489</v>
+      </c>
+      <c r="E58" t="n">
+        <v>109</v>
+      </c>
+      <c r="F58" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-0.12%</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>-14</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-14</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-11</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.02000000000000003</v>
+      </c>
+      <c r="N58" t="n">
+        <v>19.11125</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W58" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="X58" t="n">
+        <v>-4.25</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.08506841165972645</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>-3.166666666666667</v>
+      </c>
+      <c r="AC58" t="n">
+        <v>-2.060000000000002</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>-0.1014778325123153</v>
+      </c>
+      <c r="AE58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK58" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
